--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0052.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0052.xlsx
@@ -8569,7 +8569,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Lúc đó, ta đã thề rằng nếu ta trở thành thuyền trưởng, mọi thành viên trong đoàn sẽ trở về an toàn. Không có ngoại lệ.</t>
+          <t>Lúc đó, tao đã thề rằng nếu tao trở thành thuyền trưởng, mọi thành viên trong đoàn sẽ trở về an toàn. Không có ngoại lệ.</t>
         </is>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Ta không coi trọng hắn... rồi để Bella cướp mất luôn.</t>
+          <t>Tao không coi trọng hắn... rồi để Bella cướp mất luôn.</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Còn đồng xu may mắn mà ta giành giật đến đứt cả răng ấy à? Bị trộm mất rồi! Một tên trộm đáng khinh cướp mất nó. Từ đó đến giờ ta cứ như bị nguyền rủa vậy.</t>
+          <t>Còn đồng xu may mắn mà tao giành giật đến đứt cả răng ấy à? Bị trộm mất rồi! Một tên trộm đáng khinh cướp mất nó. Từ đó đến giờ tao cứ như bị nguyền rủa vậy.</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Đúng vậy, ta thua cuộc đàng hoàng. Giờ ta chỉ là một tên thủy thủ quèn thôi.</t>
+          <t>Đúng vậy, tao thua cuộc đàng hoàng. Giờ tao chỉ là một tên thủy thủ quèn thôi.</t>
         </is>
       </c>
     </row>
@@ -11689,7 +11689,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Hừm, một tên trộm tầm thường thôi... Đội trưởng à, ta có kế hoạch, nhưng lần này cậu phải lái tàu đấy.</t>
+          <t>Hừm, một tên trộm tầm thường thôi... Đội trưởng à, tao có kế hoạch, nhưng lần này cậu phải lái tàu đấy.</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>...Chết tiệt! Được rồi! Ta biết nửa còn lại ở đâu, nhưng anh phải trả giá trước đã.</t>
+          <t>...Chết tiệt! Được rồi! Tao biết nửa còn lại ở đâu, nhưng anh phải trả giá trước đã.</t>
         </is>
       </c>
     </row>
@@ -14874,7 +14874,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Ta tưởng cậu say rồi.</t>
+          <t>Tao tưởng cậu say rồi.</t>
         </is>
       </c>
     </row>
@@ -15329,7 +15329,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Cứ cho là xui xẻo một chút đi. Không thì mấy người chắc chẳng bao giờ bắt được ta đâu.</t>
+          <t>Cứ cho là xui xẻo một chút đi. Không thì mấy người chắc chẳng bao giờ bắt được tao đâu.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Ngây thơ? Ngươi ăn cắp tiền của ta, giờ còn dám nói mình vô tội?</t>
+          <t>Ngây thơ? Mày ăn cắp tiền của tao, giờ còn dám nói mình vô tội?</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Đi ngay! Ta đưa ngươi đến Tòa Án. Ngươi sẽ phải trả lại từng thứ ngươi đã cướp, và còn hơn thế nữa!</t>
+          <t>Đi ngay! Tao đưa mày đến Tòa Án. Mày sẽ phải trả lại từng thứ mày đã cướp, và còn hơn thế nữa!</t>
         </is>
       </c>
     </row>
@@ -16824,7 +16824,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Dù ta rất muốn chạy sang châm ngòi cho cuộc vui của tụi nó...</t>
+          <t>Dù tao rất muốn chạy sang châm ngòi cho cuộc vui của tụi nó...</t>
         </is>
       </c>
     </row>
@@ -17019,7 +17019,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Đúng ý ta luôn. Thấy mấy cái Echo đằng kia không?</t>
+          <t>Đúng ý tao luôn. Thấy mấy cái Echo đằng kia không?</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Tsk, đây đâu phải rượu thường. Đây là thứ ngon nhất từ thị trấn Egla đấy! Tốn của ta cả đống tiền, biết không.</t>
+          <t>Tsk, đây đâu phải rượu thường. Đây là thứ ngon nhất từ thị trấn Egla đấy! Tốn của tao cả đống tiền, biết không.</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18189,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -18579,7 +18579,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Battier tự coi mình là đối thủ của ta, nên hắn mới đem cả kho rượu lúa mì quý của mình ra đánh cược đấy.</t>
+          <t>Battier tự coi mình là đối thủ của tao, nên hắn mới đem cả kho rượu lúa mì quý của mình ra đánh cược đấy.</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18644,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Tin ta đi, thứ đó ở Thị trấn Egla ngon tuyệt cú mèo—ngọt mượt, ngon... Ta như đã nếm thử rồi ấy.</t>
+          <t>Tin tao đi, thứ đó ở Thị trấn Egla ngon tuyệt cú mèo—ngọt mượt, ngon... Tao như đã nếm thử rồi ấy.</t>
         </is>
       </c>
     </row>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Tự tin lắm à? Để ta làm cho cuộc chơi thêm phần hấp dẫn. Ta sẽ ném thêm một chai Troupe Strength vào đây. Tối nay ai cũng sẽ được phần thưởng hậu hĩ!</t>
+          <t>Tự tin lắm à? Để tao làm cho cuộc chơi thêm phần hấp dẫn. Tao sẽ ném thêm một chai Troupe Strength vào đây. Tối nay ai cũng sẽ được phần thưởng hậu hĩ!</t>
         </is>
       </c>
     </row>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Thỏa thuận! Lâu rồi ta chưa nấu ăn cho cả đội. Nếu thua, ta sẽ cho tụi bay thấy thuyền trưởng này có thể làm gì trong bếp!</t>
+          <t>Thỏa thuận! Lâu rồi tao chưa nấu ăn cho cả đội. Nếu thua, tao sẽ cho tụi bay thấy thuyền trưởng này có thể làm gì trong bếp!</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Nhìn con cá to {Male=ông ấy;Female=bà ấy} câu được kìa! Tôi dám nói Laureate của chúng ta đủ tài cán để lèo lái con tàu này!</t>
+          <t>Nhìn con cá to {Male=he;Female=she} câu được kìa! Tôi dám nói Laureate của chúng ta đủ tài cán để lèo lái con tàu này!</t>
         </is>
       </c>
     </row>
@@ -20854,7 +20854,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Cậu hiểu ý con bé nói gì không?</t>
+          <t>Mày hiểu ý con bé nói gì không?</t>
         </is>
       </c>
     </row>
@@ -20984,7 +20984,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Ừ, ta học được vài câu tiếng Echo từ Pan Cake.</t>
+          <t>Ừ, tao học được vài câu tiếng Echo từ Pan Cake.</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Ta nói thật đó, tin này lớn lắm, anh bạn ơi! Ta nghe trực tiếp từ thuyền trưởng luôn!</t>
+          <t>Tao nói thật đó, tin này lớn lắm, anh bạn ơi! Tao nghe trực tiếp từ thuyền trưởng luôn!</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Còn ta, ta sẽ lôi cổ mấy tên quý tộc Ragunna kiêu ngạo lên tàu như lũ chó ghẻ chúng nó! Chúng sẽ phải gọi ta là thuyền trưởng và cầu xin được hôn giày ta!</t>
+          <t>Còn tao, tao sẽ lôi cổ mấy tên quý tộc Ragunna kiêu ngạo lên tàu như lũ chó ghẻ chúng nó! Chúng sẽ phải gọi tao là thuyền trưởng và cầu xin được hôn giày tao!</t>
         </is>
       </c>
     </row>
@@ -24754,7 +24754,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Đồ ngốc! Ngươi không thấy à? Chúng đâu phải Lottie Lost và Cuddle Wuddle thật! Chỉ là lũ người giả dạng thôi!</t>
+          <t>Đồ ngốc! Mày không thấy à? Chúng đâu phải Lottie Lost và Cuddle Wuddle thật! Chỉ là lũ người giả dạng thôi!</t>
         </is>
       </c>
     </row>
@@ -25729,7 +25729,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Ta có linh cảm là chúng ta sẽ sớm gặp lại Aldric thôi.</t>
+          <t>Tao có linh cảm là chúng ta sẽ sớm gặp lại Aldric thôi.</t>
         </is>
       </c>
     </row>
@@ -26379,7 +26379,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Bản đồ này đánh dấu ba hòn đảo. Ta cá là đây chính là nơi Drake giấu kho báu.</t>
+          <t>Bản đồ này đánh dấu ba hòn đảo. Tao cá là đây chính là nơi Drake giấu kho báu.</t>
         </is>
       </c>
     </row>
@@ -26899,7 +26899,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Ha, đúng y như ta nghĩ.</t>
+          <t>Ha, đúng y như tao nghĩ.</t>
         </is>
       </c>
     </row>
@@ -27809,7 +27809,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Mỗi khi mọi thứ lặng im thế này, ta lại không khỏi chờ đợi màn kế tiếp và những bất ngờ nó mang đến.</t>
+          <t>Mỗi khi mọi thứ lặng im thế này, tao lại không khỏi chờ đợi màn kế tiếp và những bất ngờ nó mang đến.</t>
         </is>
       </c>
     </row>
@@ -28459,7 +28459,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi—cái xẻng đáng tin cậy của ta và chút không khí thôi.</t>
+          <t>Tất nhiên rồi—cái xẻng đáng tin cậy của tao và chút không khí thôi.</t>
         </is>
       </c>
     </row>
@@ -28979,7 +28979,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Đừng lo. Ra biển thì chuyện này thường xảy ra thôi. Cứ tin vào tay lái của mình và tin ta là được.</t>
+          <t>Đừng lo. Ra biển thì chuyện này thường xảy ra thôi. Cứ tin vào tay lái của mình và tin tao là được.</t>
         </is>
       </c>
     </row>
@@ -31254,7 +31254,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Gì!? Sao không nói sớm hơn?! Chúng ta đầu hàng! Đầu hàng!</t>
+          <t>Gì!? Sao không nói sớm hơn?! Chúng tao đầu hàng! Đầu hàng!</t>
         </is>
       </c>
     </row>
@@ -31709,7 +31709,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>A, thì ra đây là thân phận bí mật của ta!</t>
+          <t>A, thì ra đây là thân phận bí mật của tao!</t>
         </is>
       </c>
     </row>
@@ -31839,7 +31839,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Thôi đừng có giả nai! Ngươi biết ta đang nói gì mà! Đó là câu chuyện mà bất cứ thủy thủ nào cũng từng nghe!</t>
+          <t>Thôi đừng có giả nai! Mày biết tao đang nói gì mà! Đó là câu chuyện mà bất cứ thủy thủ nào cũng từng nghe!</t>
         </is>
       </c>
     </row>
@@ -32359,7 +32359,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Vàng ơi là vàng, đừng làm vậy! Ta sẽ khai hết!</t>
+          <t>Vàng ơi là vàng, đừng làm vậy! Tao sẽ khai hết!</t>
         </is>
       </c>
     </row>
@@ -32489,7 +32489,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Đồ ngốc! Ngươi không nghe đội trưởng nói à? "Ai dám cản đường chúng ta, cho chúng nó biết thế nào là hối hận!"</t>
+          <t>Đồ ngốc! Mày không nghe đội trưởng nói à? "Ai dám cản đường chúng ta, cho chúng nó biết thế nào là hối hận!"</t>
         </is>
       </c>
     </row>
